--- a/GearSage-client/rate/excel/brand.xlsx
+++ b/GearSage-client/rate/excel/brand.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Xiaochengxu\Diaoyoushuo\rate\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5317CE80-908B-4589-8789-BF12004848BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="1474" yWindow="1474" windowWidth="22166" windowHeight="14083" xr2:uid="{3B89A84E-4C4B-495E-B709-78C53F606BB0}"/>
+    <workbookView windowWidth="30240" windowHeight="14640"/>
   </bookViews>
   <sheets>
     <sheet name="brand" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>id</t>
   </si>
@@ -34,6 +41,9 @@
     <t>description</t>
   </si>
   <si>
+    <t>name_jp</t>
+  </si>
+  <si>
     <t>name_zh</t>
   </si>
   <si>
@@ -88,54 +98,138 @@
     <t>https://www.daiwa.com/</t>
   </si>
   <si>
-    <t>Pure Fishing</t>
+    <t>ABU Garcia</t>
   </si>
   <si>
     <t>是世界上唯一一家在鱼线、鱼饵、鱼竿、和附件等诸多领域拥有众多深受信赖的优质、领先品牌的渔具公司。</t>
   </si>
   <si>
-    <t>纯钓</t>
+    <t>阿布加西亚</t>
   </si>
   <si>
     <t>USA</t>
   </si>
   <si>
-    <t>name_jp</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>大河奔流</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>lurefans</t>
   </si>
   <si>
     <t>鸦语</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>lurefans</t>
   </si>
   <si>
     <t>O.S.P</t>
+  </si>
+  <si>
+    <t>Megabass</t>
+  </si>
+  <si>
+    <t>Deps</t>
+  </si>
+  <si>
+    <t>EverGreen Intl.</t>
+  </si>
+  <si>
+    <t>Frog / Toy Machine</t>
+  </si>
+  <si>
+    <t>Gan Craft</t>
+  </si>
+  <si>
+    <t>Isuzu</t>
+  </si>
+  <si>
+    <t>K.T.F.</t>
+  </si>
+  <si>
+    <t>Smith Ltd.</t>
+  </si>
+  <si>
+    <t>Tailwalk</t>
+  </si>
+  <si>
+    <t>ZPI</t>
+  </si>
+  <si>
+    <t>Olympic</t>
+  </si>
+  <si>
+    <t>Nories</t>
+  </si>
+  <si>
+    <t>Jackall</t>
+  </si>
+  <si>
+    <t>Raid Japan</t>
+  </si>
+  <si>
+    <t>Huerco</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <name val="PingFang SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="PingFang SC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -143,16 +237,22 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="等线 Light"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -161,7 +261,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -170,7 +269,52 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -178,7 +322,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -186,7 +329,6 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -194,105 +336,15 @@
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="PingFang SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="PingFang SC"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -304,175 +356,188 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -482,6 +547,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -507,7 +587,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -542,15 +622,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -566,17 +637,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -592,200 +657,227 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -834,7 +926,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -867,26 +959,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -919,23 +994,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1077,29 +1135,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E15F06E8-B549-4886-9D5C-98841BE44990}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="29.35546875" customWidth="1"/>
-    <col min="5" max="5" width="23.2109375" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" customWidth="1"/>
-    <col min="8" max="8" width="23.140625" customWidth="1"/>
-    <col min="9" max="9" width="14.35546875" customWidth="1"/>
-    <col min="10" max="10" width="10.640625" customWidth="1"/>
+    <col min="2" max="2" width="23.0625" customWidth="1"/>
+    <col min="3" max="3" width="18.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="29.3571428571429" customWidth="1"/>
+    <col min="5" max="5" width="23.2142857142857" customWidth="1"/>
+    <col min="6" max="6" width="20.1428571428571" customWidth="1"/>
+    <col min="7" max="7" width="11.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="23.1428571428571" customWidth="1"/>
+    <col min="9" max="9" width="14.3571428571429" customWidth="1"/>
+    <col min="10" max="10" width="10.6428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1116,22 +1169,22 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1139,25 +1192,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1166,25 +1219,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1193,19 +1246,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1216,7 +1269,7 @@
         <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1224,7 +1277,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1235,9 +1288,133 @@
         <v>30</v>
       </c>
     </row>
+    <row r="8" spans="1:10">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B20" r:id="rId1" display="Jackall" tooltip="https://jdmfishing.com/product-category/rods/jackall-rods/"/>
+    <hyperlink ref="B22" r:id="rId2" display="Huerco" tooltip="https://jdmfishing.com/product-category/rods/huerco/"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/brand.xlsx
+++ b/GearSage-client/rate/excel/brand.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="135">
   <si>
     <t>id</t>
   </si>
@@ -125,46 +125,313 @@
     <t>Megabass</t>
   </si>
   <si>
+    <t>13 Fishing</t>
+  </si>
+  <si>
+    <t>Accurate</t>
+  </si>
+  <si>
+    <t>AFTCO</t>
+  </si>
+  <si>
+    <t>Berkley</t>
+  </si>
+  <si>
+    <t>Columbia PFG</t>
+  </si>
+  <si>
     <t>Deps</t>
   </si>
   <si>
-    <t>EverGreen Intl.</t>
+    <t>DUO</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>Fox Rage / Fox</t>
   </si>
   <si>
     <t>Frog / Toy Machine</t>
   </si>
   <si>
+    <t>FXR</t>
+  </si>
+  <si>
+    <t>Gamakatsu</t>
+  </si>
+  <si>
     <t>Gan Craft</t>
   </si>
   <si>
+    <t>Gary Yamamoto</t>
+  </si>
+  <si>
+    <t>Gill</t>
+  </si>
+  <si>
+    <t>Grundéns</t>
+  </si>
+  <si>
+    <t>Huerco</t>
+  </si>
+  <si>
+    <t>Huk</t>
+  </si>
+  <si>
+    <t>ima</t>
+  </si>
+  <si>
+    <t>Imakatsu</t>
+  </si>
+  <si>
+    <t>Ism / Infinite Blade</t>
+  </si>
+  <si>
     <t>Isuzu</t>
   </si>
   <si>
+    <t>JA-DO</t>
+  </si>
+  <si>
+    <t>Jackall</t>
+  </si>
+  <si>
+    <t>Jackson</t>
+  </si>
+  <si>
     <t>K.T.F.</t>
   </si>
   <si>
+    <t>KAWA</t>
+  </si>
+  <si>
+    <t>Keitech</t>
+  </si>
+  <si>
+    <t>Legit Design</t>
+  </si>
+  <si>
+    <t>Lew’s</t>
+  </si>
+  <si>
+    <t>Lucky Craft</t>
+  </si>
+  <si>
+    <t>Major Craft</t>
+  </si>
+  <si>
+    <t>Mibro</t>
+  </si>
+  <si>
+    <t>Musto</t>
+  </si>
+  <si>
+    <t>N.S</t>
+  </si>
+  <si>
+    <t>Noike</t>
+  </si>
+  <si>
+    <t>Nories</t>
+  </si>
+  <si>
+    <t>Okuma</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>palms / 小椰树</t>
+  </si>
+  <si>
+    <t>Patagonia</t>
+  </si>
+  <si>
+    <t>Pelagic</t>
+  </si>
+  <si>
+    <t>Penn</t>
+  </si>
+  <si>
+    <t>Phat Lab</t>
+  </si>
+  <si>
+    <t>Piscifun</t>
+  </si>
+  <si>
+    <t>Power Pro</t>
+  </si>
+  <si>
+    <t>Raid Japan</t>
+  </si>
+  <si>
+    <t>Rapala</t>
+  </si>
+  <si>
+    <t>Ripple Fisher</t>
+  </si>
+  <si>
+    <t>RomanMade</t>
+  </si>
+  <si>
+    <t>Seaguar</t>
+  </si>
+  <si>
+    <t>Sedition</t>
+  </si>
+  <si>
+    <t>Simms</t>
+  </si>
+  <si>
     <t>Smith Ltd.</t>
   </si>
   <si>
+    <t>Studio Composite / I.D.</t>
+  </si>
+  <si>
+    <t>Sufix</t>
+  </si>
+  <si>
     <t>Tailwalk</t>
   </si>
   <si>
+    <t>Taper &amp; Shape</t>
+  </si>
+  <si>
+    <t>Tenryu</t>
+  </si>
+  <si>
+    <t>Tiemco / Fenwick</t>
+  </si>
+  <si>
+    <t>Tulala</t>
+  </si>
+  <si>
+    <t>Vagabond</t>
+  </si>
+  <si>
+    <t>Valley Hill/Mission Tackle</t>
+  </si>
+  <si>
+    <t>Van Staal</t>
+  </si>
+  <si>
+    <t>Varivas</t>
+  </si>
+  <si>
+    <t>Whiplash Factory</t>
+  </si>
+  <si>
+    <t>Yamaga Blanks</t>
+  </si>
+  <si>
+    <t>YGK</t>
+  </si>
+  <si>
+    <t>Yo-Zuri / Duel</t>
+  </si>
+  <si>
+    <t>Zenaq</t>
+  </si>
+  <si>
+    <t>ZipBaits</t>
+  </si>
+  <si>
     <t>ZPI</t>
   </si>
   <si>
-    <t>Olympic</t>
-  </si>
-  <si>
-    <t>Nories</t>
-  </si>
-  <si>
-    <t>Jackall</t>
-  </si>
-  <si>
-    <t>Raid Japan</t>
-  </si>
-  <si>
-    <t>Huerco</t>
+    <t>东丽 Toray</t>
+  </si>
+  <si>
+    <t>光威</t>
+  </si>
+  <si>
+    <t>凯霖</t>
+  </si>
+  <si>
+    <t>北溟鱼</t>
+  </si>
+  <si>
+    <t>卡斯丁</t>
+  </si>
+  <si>
+    <t>品钓</t>
+  </si>
+  <si>
+    <t>哈斯达</t>
+  </si>
+  <si>
+    <t>喜曼多 SIMAGO</t>
+  </si>
+  <si>
+    <t>国王路亚</t>
+  </si>
+  <si>
+    <t>宝飞龙</t>
+  </si>
+  <si>
+    <t>巨帝</t>
+  </si>
+  <si>
+    <t>摩利根 Morigen</t>
+  </si>
+  <si>
+    <t>桑濑 Sunline</t>
+  </si>
+  <si>
+    <t>汉鼎</t>
+  </si>
+  <si>
+    <t>海伯</t>
+  </si>
+  <si>
+    <t>海龙王</t>
+  </si>
+  <si>
+    <t>熊王</t>
+  </si>
+  <si>
+    <t>爱克飞丝 AKFS</t>
+  </si>
+  <si>
+    <t>盛河</t>
+  </si>
+  <si>
+    <t>科尼</t>
+  </si>
+  <si>
+    <t>美人鱼</t>
+  </si>
+  <si>
+    <t>美夏 EWE</t>
+  </si>
+  <si>
+    <t>翠鸟</t>
+  </si>
+  <si>
+    <t>蓝旗鱼</t>
+  </si>
+  <si>
+    <t>路亚发烧友</t>
+  </si>
+  <si>
+    <t>钓之屋</t>
+  </si>
+  <si>
+    <t>钓邦</t>
+  </si>
+  <si>
+    <t>钓鱼王</t>
+  </si>
+  <si>
+    <t>领峰</t>
+  </si>
+  <si>
+    <t>飞蚂蚁</t>
+  </si>
+  <si>
+    <t>高森 Gosen</t>
   </si>
 </sst>
 </file>
@@ -177,7 +444,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,19 +463,6 @@
       <color theme="1"/>
       <name val="PingFang SC"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.8"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -661,19 +915,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -682,58 +945,49 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -745,7 +999,7 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -757,7 +1011,7 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -769,7 +1023,7 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -781,7 +1035,7 @@
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -793,7 +1047,7 @@
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -806,7 +1060,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -817,9 +1071,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -874,6 +1125,18 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1141,7 +1404,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="23.0625" customWidth="1"/>
@@ -1388,7 +1651,7 @@
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1404,15 +1667,726 @@
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" t="s">
         <v>45</v>
       </c>
     </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B20" r:id="rId1" display="Jackall" tooltip="https://jdmfishing.com/product-category/rods/jackall-rods/"/>
-    <hyperlink ref="B22" r:id="rId2" display="Huerco" tooltip="https://jdmfishing.com/product-category/rods/huerco/"/>
-  </hyperlinks>
+  <conditionalFormatting sqref="B1:B8 B113:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/GearSage-client/rate/excel/brand.xlsx
+++ b/GearSage-client/rate/excel/brand.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="136">
   <si>
     <t>id</t>
   </si>
@@ -432,6 +432,9 @@
   </si>
   <si>
     <t>高森 Gosen</t>
+  </si>
+  <si>
+    <t>BKK</t>
   </si>
 </sst>
 </file>
@@ -1404,7 +1407,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="23.0625" customWidth="1"/>
@@ -2383,6 +2386,14 @@
         <v>134</v>
       </c>
     </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B8 B113:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/GearSage-client/rate/excel/brand.xlsx
+++ b/GearSage-client/rate/excel/brand.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="138">
   <si>
     <t>id</t>
   </si>
@@ -435,6 +435,12 @@
   </si>
   <si>
     <t>BKK</t>
+  </si>
+  <si>
+    <t>Mustad</t>
+  </si>
+  <si>
+    <t>慕斯达</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="23.0625" customWidth="1"/>
@@ -2394,6 +2400,17 @@
         <v>135</v>
       </c>
     </row>
+    <row r="113" spans="1:6">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>136</v>
+      </c>
+      <c r="F113" t="s">
+        <v>137</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B8 B113:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/GearSage-client/rate/excel/brand.xlsx
+++ b/GearSage-client/rate/excel/brand.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="14640"/>
+    <workbookView windowWidth="30240" windowHeight="12940"/>
   </bookViews>
   <sheets>
     <sheet name="brand" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
     <t>https://www.daiwa.com/</t>
   </si>
   <si>
-    <t>ABU Garcia</t>
+    <t>Abu Garcia</t>
   </si>
   <si>
     <t>是世界上唯一一家在鱼线、鱼饵、鱼竿、和附件等诸多领域拥有众多深受信赖的优质、领先品牌的渔具公司。</t>
@@ -2412,8 +2412,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C4">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B1:B8 B113:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/GearSage-client/rate/excel/brand.xlsx
+++ b/GearSage-client/rate/excel/brand.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12940"/>
+    <workbookView windowWidth="25420" windowHeight="12940"/>
   </bookViews>
   <sheets>
     <sheet name="brand" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="139">
   <si>
     <t>id</t>
   </si>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>慕斯达</t>
+  </si>
+  <si>
+    <t>Olympic</t>
   </si>
 </sst>
 </file>
@@ -1413,7 +1416,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="23.0625" customWidth="1"/>
@@ -2411,6 +2414,14 @@
         <v>137</v>
       </c>
     </row>
+    <row r="114" spans="1:6">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C4">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/GearSage-client/rate/excel/brand.xlsx
+++ b/GearSage-client/rate/excel/brand.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="140">
   <si>
     <t>id</t>
   </si>
@@ -444,6 +444,9 @@
   </si>
   <si>
     <t>Olympic</t>
+  </si>
+  <si>
+    <t>Dstyle</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1419,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J114"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="23.0625" customWidth="1"/>
@@ -2422,6 +2425,14 @@
         <v>138</v>
       </c>
     </row>
+    <row r="115" spans="1:6">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>139</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C4">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/GearSage-client/rate/excel/brand.xlsx
+++ b/GearSage-client/rate/excel/brand.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="141">
   <si>
     <t>id</t>
   </si>
@@ -447,6 +447,9 @@
   </si>
   <si>
     <t>Dstyle</t>
+  </si>
+  <si>
+    <t>Ark</t>
   </si>
 </sst>
 </file>
@@ -1419,7 +1422,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J115"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="23.0625" customWidth="1"/>
@@ -2433,6 +2436,14 @@
         <v>139</v>
       </c>
     </row>
+    <row r="116" spans="1:6">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C4">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
